--- a/toy-rulebooks/star-trek/xlsx/rulebook.xlsx
+++ b/toy-rulebooks/star-trek/xlsx/rulebook.xlsx
@@ -17,6 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratings" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERBVersions" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERBCustomizations" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="__meta__" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -158,6 +159,41 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>The metadata key (e.g. 'tagline', 'motif_palette', 'substrates'). Unique within the table.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Identifier for this metadata entry. Mirrors MetaKey so the row is addressable by Name like every other table.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>How to interpret the value columns: 'string' (use StringValue), 'object' (parse JsonValue as JSON object), 'array' (parse JsonValue as JSON array).</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Plain string value. Populated when ValueType == 'string'; null otherwise.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>JSON-encoded value. Populated when ValueType == 'object' or 'array'; null when ValueType == 'string'.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1676,6 +1712,275 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MetaKey</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ValueType</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>StringValue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>JsonValue</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>tagline</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>$A2</f>
+        <v/>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Ten Star Trek shows, hundreds of episodes, fan ratings — and roll-ups that survive a re-canon.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>motif</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>$A3</f>
+        <v/>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>lcars</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>motif_palette</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>$A4</f>
+        <v/>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>{"primary": "#663d6b", "accent": "#ff9966", "ink": "#1a0d20"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>description_rich</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>$A5</f>
+        <v/>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>A media catalog of the entire **Star Trek** television franchise — ten series from *TOS* through *Strange New Worlds*, every season, every episode, every fan rating. The interesting thing isn't the catalog, it's the **roll-ups**: `Episodes` count up into `Seasons.EpisodeCount`, those counts sum up into `Series.TotalEpisodes`, and individual `Ratings` average up into `Series.Rating`. Derived booleans like `IsLongRunning` (more than 50 episodes) and `IsGood` (average rating ≥ 4.5) sit on top — change a single rating, and every level of the hierarchy re-derives identically in Postgres, Python, Excel, and OWL.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>use_cases</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>$A6</f>
+        <v/>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>["**Add a 5-star *TOS* rating** and watch `Series.Rating` climb from `4.33` to exactly `4.5` — `IsGood` flips from `FALSE` to `TRUE` on the next read, with no application code in between.", "**Lower the *long-running* threshold** from `50` episodes to `25` and *Lower Decks* (42 episodes) instantly joins the long-running club; *Strange New Worlds* (20) stays a newcomer.", "**Reassign an episode to a different season** — `Seasons.EpisodeCount` shifts on both old and new season, and `Series.TotalEpisodes` re-derives across the whole show without a single manual update.", "**Ask *\"which series are good and long-running?\"*** in the Postgres view, then ask the same question of the generated Python module — same answer, same row order, no glue code."]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>signature_rows</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>$A7</f>
+        <v/>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>[{"entity": "Series", "ids": ["1-tos", "2-tng", "3-ds9"]}, {"entity": "Episodes", "ids": ["1-tos-season-1-episode-01", "1-tos-season-1-episode-07", "1-tos-season-1-episode-10"]}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>journal_seed</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>$A8</f>
+        <v/>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Ten shows on the bridge — TOS still the highest-rated when the votes are in; Picard and Strange New Worlds still awaiting their first ratings.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>substrates</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>$A9</f>
+        <v/>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>[{"key": "postgres", "important": true, "chip_label": "Postgres"}, {"key": "python", "important": true, "chip_label": "Python"}, {"key": "excel", "important": false, "chip_label": "Excel"}, {"key": "owl", "important": false, "chip_label": "OWL"}, {"key": "csv", "important": false, "chip_label": "CSV"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>CMCC_Summary</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <f>$A10</f>
+        <v/>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Airtable export with schema-first type mapping: Schemas, Data, Relationships (FK links), Lookups (INDEX/MATCH), Aggregations (SUMIFS/COUNTIFS/Rollups), and Calculated fields (formulas) in Excel dialect. Field types are determined from Airtable's schema metadata FIRST (no coercion); the build FAILS if metadata is unavailable rather than silently inferring from formula/data analysis.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>conversion_metadata</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>$A11</f>
+        <v/>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>{"source_base_id": "appqwWQxIWFtyDsiL", "table_count": 6, "tool_version": "2.0.0", "field_type_mapping": "checkbox→boolean, number→number/integer, multipleRecordLinks→relationship, multipleLookupValues→lookup, rollup→aggregation, count→aggregation, formula→calculated", "export_mode": "schema_first_type_mapping", "type_inference": {"enabled": true, "priority": "airtable_metadata (NO COERCION) → formula_analysis → reference_resolution → data_analysis (last-resort inference; build SHOULD FAIL rather than silently use this)", "airtable_type_mapping": "checkbox→boolean, singleLineText→string, multilineText→string, number→number/integer, datetime→datetime, singleSelect→string, email→string, url→string, phoneNumber→string", "data_coercion_hierarchy": "Only invoked when Airtable schema is unavailable (which SHOULD make the build fail). Coercion order: datetime → number → integer → boolean → base64 → json → string", "nullable_support": true, "error_value_handling": "#NUM!, #ERROR!, #N/A, #REF!, #DIV/0!, #VALUE!, #NAME? are treated as NULL"}}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
